--- a/scoring_statistics.xlsx
+++ b/scoring_statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RenpyProjects\USDebate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B5B80F54B7C21B4A3FFAF516DBD45EE231EF3F2A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D142116C-F631-4C43-919C-4BBD00842FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
